--- a/files/price-rassvet-k.xlsx
+++ b/files/price-rassvet-k.xlsx
@@ -686,7 +686,7 @@
         <v>426</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2323500</v>
+        <v>232350</v>
       </c>
     </row>
     <row r="20">
